--- a/grupos/2ASV - Estadisticos 20232.xlsx
+++ b/grupos/2ASV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
   <si>
     <t>Materia</t>
   </si>
@@ -176,6 +176,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>BASILIO</t>
   </si>
   <si>
@@ -188,6 +191,9 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -198,6 +204,9 @@
   </si>
   <si>
     <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>GIANCARLO</t>
   </si>
   <si>
     <t>CLARA LIZBETH</t>
@@ -774,31 +783,31 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -831,22 +840,22 @@
         <v>5</v>
       </c>
       <c r="AD4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE4">
         <v>6</v>
       </c>
       <c r="AF4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH4">
         <v>5</v>
       </c>
       <c r="AI4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ4">
         <v>5</v>
@@ -887,31 +896,31 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -947,19 +956,19 @@
         <v>5</v>
       </c>
       <c r="AE5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ5">
         <v>5</v>
@@ -1000,31 +1009,31 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1054,28 +1063,28 @@
         <v>-1</v>
       </c>
       <c r="AC6">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>9</v>
+      </c>
+      <c r="AE6">
+        <v>9</v>
+      </c>
+      <c r="AF6">
+        <v>9</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+      <c r="AH6">
         <v>8</v>
       </c>
-      <c r="AD6">
-        <v>8</v>
-      </c>
-      <c r="AE6">
-        <v>8</v>
-      </c>
-      <c r="AF6">
-        <v>8</v>
-      </c>
-      <c r="AG6">
-        <v>10</v>
-      </c>
-      <c r="AH6">
-        <v>6</v>
-      </c>
       <c r="AI6">
         <v>10</v>
       </c>
       <c r="AJ6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK6">
         <v>-1</v>
@@ -1113,31 +1122,31 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1182,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="AH7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI7">
         <v>10</v>
@@ -1226,31 +1235,31 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1289,10 +1298,10 @@
         <v>5</v>
       </c>
       <c r="AF8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH8">
         <v>5</v>
@@ -1339,31 +1348,31 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1405,13 +1414,13 @@
         <v>7</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH9">
         <v>5</v>
       </c>
       <c r="AI9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ9">
         <v>6</v>
@@ -1452,31 +1461,31 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1506,25 +1515,25 @@
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE10">
         <v>7</v>
       </c>
       <c r="AF10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH10">
         <v>5</v>
       </c>
       <c r="AI10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ10">
         <v>6</v>
@@ -1565,31 +1574,31 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1622,25 +1631,25 @@
         <v>10</v>
       </c>
       <c r="AD11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE11">
         <v>7</v>
       </c>
       <c r="AF11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG11">
         <v>10</v>
       </c>
       <c r="AH11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK11">
         <v>-1</v>
@@ -1678,31 +1687,31 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1791,31 +1800,31 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1848,22 +1857,22 @@
         <v>5</v>
       </c>
       <c r="AD13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE13">
         <v>6</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ13">
         <v>6</v>
@@ -1904,31 +1913,31 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1961,19 +1970,19 @@
         <v>10</v>
       </c>
       <c r="AD14">
+        <v>9</v>
+      </c>
+      <c r="AE14">
+        <v>9</v>
+      </c>
+      <c r="AF14">
+        <v>9</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+      <c r="AH14">
         <v>8</v>
-      </c>
-      <c r="AE14">
-        <v>8</v>
-      </c>
-      <c r="AF14">
-        <v>7</v>
-      </c>
-      <c r="AG14">
-        <v>10</v>
-      </c>
-      <c r="AH14">
-        <v>6</v>
       </c>
       <c r="AI14">
         <v>10</v>
@@ -2017,31 +2026,31 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2276,55 +2285,55 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O4">
-        <v>91.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="P4">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q4">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R4">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X4">
-        <v>91.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="Y4">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Z4">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AB4">
         <v>100</v>
@@ -2362,58 +2371,58 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="L5">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O5">
-        <v>91.40000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="P5">
-        <v>93.8</v>
+        <v>46.9</v>
       </c>
       <c r="Q5">
-        <v>86.7</v>
+        <v>43.3</v>
       </c>
       <c r="R5">
-        <v>80</v>
+        <v>36.4</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T5">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="U5">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="X5">
-        <v>91.40000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="Y5">
-        <v>93.8</v>
+        <v>46.9</v>
       </c>
       <c r="Z5">
-        <v>86.7</v>
+        <v>43.3</v>
       </c>
       <c r="AA5">
-        <v>80</v>
+        <v>36.4</v>
       </c>
       <c r="AB5">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -2451,7 +2460,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -2460,7 +2469,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -2469,7 +2478,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -2478,7 +2487,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -2487,7 +2496,7 @@
         <v>100</v>
       </c>
       <c r="X6">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y6">
         <v>100</v>
@@ -2496,7 +2505,7 @@
         <v>100</v>
       </c>
       <c r="AA6">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="AB6">
         <v>100</v>
@@ -2546,7 +2555,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -2573,7 +2582,7 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -2620,55 +2629,55 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O8">
-        <v>85.7</v>
+        <v>90</v>
       </c>
       <c r="P8">
+        <v>81.3</v>
+      </c>
+      <c r="Q8">
+        <v>83.3</v>
+      </c>
+      <c r="R8">
+        <v>95.5</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
+        <v>95.5</v>
+      </c>
+      <c r="U8">
+        <v>97.5</v>
+      </c>
+      <c r="V8">
         <v>75</v>
       </c>
-      <c r="Q8">
-        <v>80</v>
-      </c>
-      <c r="R8">
+      <c r="W8">
+        <v>98</v>
+      </c>
+      <c r="X8">
         <v>90</v>
       </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
-        <v>91.7</v>
-      </c>
-      <c r="U8">
-        <v>95</v>
-      </c>
-      <c r="V8">
-        <v>50</v>
-      </c>
-      <c r="W8">
-        <v>96</v>
-      </c>
-      <c r="X8">
-        <v>85.7</v>
-      </c>
       <c r="Y8">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Z8">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="AA8">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="AB8">
         <v>100</v>
@@ -2706,7 +2715,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L9">
         <v>85</v>
@@ -2715,10 +2724,10 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O9">
-        <v>88.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -2727,13 +2736,13 @@
         <v>93.3</v>
       </c>
       <c r="R9">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T9">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U9">
         <v>85</v>
@@ -2742,10 +2751,10 @@
         <v>100</v>
       </c>
       <c r="W9">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X9">
-        <v>88.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -2754,10 +2763,10 @@
         <v>93.3</v>
       </c>
       <c r="AA9">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="AB9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -2792,22 +2801,22 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -2819,22 +2828,22 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X10">
         <v>100</v>
       </c>
       <c r="Y10">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z10">
         <v>100</v>
@@ -2964,7 +2973,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2976,22 +2985,22 @@
         <v>80</v>
       </c>
       <c r="O12">
-        <v>11.4</v>
+        <v>5.7</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="R12">
         <v>0</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T12">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="U12">
         <v>0</v>
@@ -3003,19 +3012,19 @@
         <v>80</v>
       </c>
       <c r="X12">
-        <v>11.4</v>
+        <v>5.7</v>
       </c>
       <c r="Y12">
         <v>0</v>
       </c>
       <c r="Z12">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -3050,58 +3059,58 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="L13">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="M13">
         <v>100</v>
       </c>
       <c r="N13">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O13">
-        <v>97.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T13">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="U13">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="X13">
-        <v>97.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="Y13">
         <v>100</v>
       </c>
       <c r="Z13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="AA13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="AB13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -3139,25 +3148,25 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O14">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R14">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3166,25 +3175,25 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X14">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Y14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="AA14">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="AB14">
         <v>100</v>
@@ -3222,58 +3231,58 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M15">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N15">
         <v>80</v>
       </c>
       <c r="O15">
-        <v>57.1</v>
+        <v>28.6</v>
       </c>
       <c r="P15">
-        <v>37.5</v>
+        <v>18.8</v>
       </c>
       <c r="Q15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="R15">
-        <v>50</v>
+        <v>22.7</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T15">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="U15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="V15">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="W15">
         <v>80</v>
       </c>
       <c r="X15">
-        <v>57.1</v>
+        <v>28.6</v>
       </c>
       <c r="Y15">
-        <v>37.5</v>
+        <v>18.8</v>
       </c>
       <c r="Z15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA15">
-        <v>50</v>
+        <v>22.7</v>
       </c>
       <c r="AB15">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3368,19 +3377,19 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
       <c r="G3" s="2">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3412,7 +3421,7 @@
         <v>58.3</v>
       </c>
       <c r="H4">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3444,7 +3453,7 @@
         <v>41.7</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3464,19 +3473,19 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="G6" s="2">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3496,19 +3505,19 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="G7" s="2">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3540,7 +3549,7 @@
         <v>25</v>
       </c>
       <c r="H8">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3572,7 +3581,7 @@
         <v>25</v>
       </c>
       <c r="H9">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3604,7 +3613,7 @@
         <v>16.7</v>
       </c>
       <c r="H10">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -3654,7 +3663,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3686,39 +3695,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920287</v>
+        <v>23330051920300</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920288</v>
+        <v>23330051920300</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
         <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -3732,16 +3741,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920302</v>
+        <v>23330051920287</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
         <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -3755,16 +3764,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920304</v>
+        <v>23330051920288</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
         <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -3773,6 +3782,52 @@
         <v>39</v>
       </c>
       <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920302</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920304</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20232.xlsx
+++ b/grupos/2ASV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -143,27 +143,27 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -176,43 +176,79 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>CLARA LIZBETH</t>
+  </si>
+  <si>
+    <t>HEIDI KESEI</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>JULIO ALBERTO</t>
+  </si>
+  <si>
     <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
   </si>
   <si>
     <t>ANA ISABEL</t>
@@ -810,40 +846,40 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>-1</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF4">
         <v>8</v>
@@ -852,13 +888,13 @@
         <v>8</v>
       </c>
       <c r="AH4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI4">
         <v>8</v>
       </c>
       <c r="AJ4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK4">
         <v>-1</v>
@@ -923,28 +959,28 @@
         <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB5">
         <v>-1</v>
@@ -956,19 +992,19 @@
         <v>5</v>
       </c>
       <c r="AE5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF5">
         <v>5</v>
       </c>
       <c r="AG5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AH5">
         <v>5</v>
       </c>
       <c r="AI5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ5">
         <v>5</v>
@@ -1036,28 +1072,28 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB6">
         <v>-1</v>
@@ -1078,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="AH6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI6">
         <v>10</v>
@@ -1149,28 +1185,28 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB7">
         <v>-1</v>
@@ -1191,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="AH7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI7">
         <v>10</v>
@@ -1262,55 +1298,55 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK8">
         <v>-1</v>
@@ -1375,49 +1411,49 @@
         <v>5</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>-1</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE9">
         <v>7</v>
       </c>
       <c r="AF9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI9">
         <v>7</v>
@@ -1488,37 +1524,37 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB10">
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE10">
         <v>7</v>
@@ -1527,13 +1563,13 @@
         <v>8</v>
       </c>
       <c r="AG10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ10">
         <v>6</v>
@@ -1601,28 +1637,28 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>-1</v>
@@ -1643,7 +1679,7 @@
         <v>10</v>
       </c>
       <c r="AH11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI11">
         <v>9</v>
@@ -1714,28 +1750,28 @@
         <v>5</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB12">
         <v>-1</v>
@@ -1827,28 +1863,28 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>-1</v>
@@ -1857,10 +1893,10 @@
         <v>5</v>
       </c>
       <c r="AD13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF13">
         <v>7</v>
@@ -1869,7 +1905,7 @@
         <v>7</v>
       </c>
       <c r="AH13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI13">
         <v>8</v>
@@ -1940,34 +1976,34 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>-1</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD14">
         <v>9</v>
@@ -1982,7 +2018,7 @@
         <v>10</v>
       </c>
       <c r="AH14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI14">
         <v>10</v>
@@ -2053,28 +2089,28 @@
         <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB15">
         <v>-1</v>
@@ -2312,28 +2348,28 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U4">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X4">
-        <v>95.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y4">
         <v>93.8</v>
       </c>
       <c r="Z4">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="AA4">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AB4">
         <v>100</v>
@@ -2398,28 +2434,28 @@
         <v>90.59999999999999</v>
       </c>
       <c r="T5">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="U5">
-        <v>55</v>
+        <v>36.7</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>84</v>
+        <v>52.5</v>
       </c>
       <c r="X5">
-        <v>54.3</v>
+        <v>33.9</v>
       </c>
       <c r="Y5">
-        <v>46.9</v>
+        <v>31.3</v>
       </c>
       <c r="Z5">
-        <v>43.3</v>
+        <v>27.1</v>
       </c>
       <c r="AA5">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="AB5">
         <v>90.59999999999999</v>
@@ -2487,7 +2523,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -2496,7 +2532,7 @@
         <v>100</v>
       </c>
       <c r="X6">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="Y6">
         <v>100</v>
@@ -2505,7 +2541,7 @@
         <v>100</v>
       </c>
       <c r="AA6">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="AB6">
         <v>100</v>
@@ -2582,7 +2618,7 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -2656,28 +2692,28 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U8">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V8">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="W8">
-        <v>98</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="X8">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y8">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Z8">
-        <v>83.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AA8">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB8">
         <v>100</v>
@@ -2742,28 +2778,28 @@
         <v>93.8</v>
       </c>
       <c r="T9">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U9">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V9">
         <v>100</v>
       </c>
       <c r="W9">
-        <v>98</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X9">
-        <v>87.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="Y9">
         <v>100</v>
       </c>
       <c r="Z9">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="AA9">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="AB9">
         <v>93.8</v>
@@ -2828,22 +2864,22 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U10">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X10">
         <v>100</v>
       </c>
       <c r="Y10">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Z10">
         <v>100</v>
@@ -2926,7 +2962,7 @@
         <v>100</v>
       </c>
       <c r="X11">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -3000,7 +3036,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="T12">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="U12">
         <v>0</v>
@@ -3009,16 +3045,16 @@
         <v>0</v>
       </c>
       <c r="W12">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="X12">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y12">
         <v>0</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AA12">
         <v>0</v>
@@ -3086,28 +3122,28 @@
         <v>93.8</v>
       </c>
       <c r="T13">
-        <v>81.8</v>
+        <v>75</v>
       </c>
       <c r="U13">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>93</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="X13">
-        <v>94.3</v>
+        <v>92</v>
       </c>
       <c r="Y13">
         <v>100</v>
       </c>
       <c r="Z13">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA13">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB13">
         <v>93.8</v>
@@ -3175,25 +3211,25 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X14">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="Y14">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="Z14">
+        <v>95.8</v>
+      </c>
+      <c r="AA14">
         <v>96.90000000000001</v>
-      </c>
-      <c r="Z14">
-        <v>93.3</v>
-      </c>
-      <c r="AA14">
-        <v>95.5</v>
       </c>
       <c r="AB14">
         <v>100</v>
@@ -3258,28 +3294,28 @@
         <v>90.59999999999999</v>
       </c>
       <c r="T15">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="U15">
-        <v>97.5</v>
+        <v>73.3</v>
       </c>
       <c r="V15">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="W15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="X15">
-        <v>28.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y15">
-        <v>18.8</v>
+        <v>12.5</v>
       </c>
       <c r="Z15">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AA15">
-        <v>22.7</v>
+        <v>15.6</v>
       </c>
       <c r="AB15">
         <v>90.59999999999999</v>
@@ -3377,19 +3413,19 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="G3" s="2">
-        <v>58.3</v>
+        <v>33.3</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3400,7 +3436,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -3409,19 +3445,19 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>41.7</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2">
-        <v>58.3</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3432,7 +3468,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>42</v>
@@ -3441,19 +3477,19 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>58.3</v>
+        <v>75</v>
       </c>
       <c r="G5" s="2">
-        <v>41.7</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3464,7 +3500,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -3473,19 +3509,19 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G6" s="2">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3496,7 +3532,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
@@ -3505,19 +3541,19 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3528,7 +3564,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>45</v>
@@ -3549,7 +3585,7 @@
         <v>25</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3560,7 +3596,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>46</v>
@@ -3581,7 +3617,7 @@
         <v>25</v>
       </c>
       <c r="H9">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3592,7 +3628,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -3613,7 +3649,7 @@
         <v>16.7</v>
       </c>
       <c r="H10">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -3663,7 +3699,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3695,22 +3731,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920300</v>
+        <v>23330051920303</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3718,16 +3754,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920300</v>
+        <v>23330051920303</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -3741,16 +3777,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920287</v>
+        <v>23330051920319</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -3764,16 +3800,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920288</v>
+        <v>23330051920287</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -3787,16 +3823,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920302</v>
+        <v>23330051920288</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -3810,16 +3846,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920304</v>
+        <v>23330051920289</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -3828,6 +3864,98 @@
         <v>39</v>
       </c>
       <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920290</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920300</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920302</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920304</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ASV - Estadisticos 20232.xlsx
+++ b/grupos/2ASV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="61">
   <si>
     <t>Materia</t>
   </si>
@@ -179,82 +179,28 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
     <t>TINOCO</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>NOHEMI ANGELICA</t>
   </si>
   <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
-  </si>
-  <si>
     <t>CRISTIAN</t>
   </si>
   <si>
     <t>JULIO ALBERTO</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>ANA ISABEL</t>
-  </si>
-  <si>
-    <t>SAUL</t>
   </si>
 </sst>
 </file>
@@ -897,7 +843,7 @@
         <v>6</v>
       </c>
       <c r="AK4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1010,7 +956,7 @@
         <v>5</v>
       </c>
       <c r="AK5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1123,7 +1069,7 @@
         <v>7</v>
       </c>
       <c r="AK6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1236,7 +1182,7 @@
         <v>8</v>
       </c>
       <c r="AK7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1349,7 +1295,7 @@
         <v>6</v>
       </c>
       <c r="AK8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1462,7 +1408,7 @@
         <v>6</v>
       </c>
       <c r="AK9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1575,7 +1521,7 @@
         <v>6</v>
       </c>
       <c r="AK10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1688,7 +1634,7 @@
         <v>7</v>
       </c>
       <c r="AK11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1801,7 +1747,7 @@
         <v>5</v>
       </c>
       <c r="AK12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1914,7 +1860,7 @@
         <v>6</v>
       </c>
       <c r="AK13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2027,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="AK14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2140,7 +2086,7 @@
         <v>5</v>
       </c>
       <c r="AK15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3384,22 +3330,25 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G2" s="2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3699,7 +3648,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3737,10 +3686,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3760,10 +3709,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -3772,21 +3721,21 @@
         <v>39</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920319</v>
+        <v>23330051920289</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -3795,21 +3744,21 @@
         <v>39</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920287</v>
+        <v>23330051920290</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -3818,145 +3767,7 @@
         <v>39</v>
       </c>
       <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920288</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920289</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920290</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920300</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920302</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920304</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ASV - Estadisticos 20232.xlsx
+++ b/grupos/2ASV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="61">
   <si>
     <t>Materia</t>
   </si>
@@ -176,31 +176,31 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
   </si>
   <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>JULIO ALBERTO</t>
   </si>
   <si>
     <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>JULIO ALBERTO</t>
   </si>
 </sst>
 </file>
@@ -816,7 +816,7 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>6</v>
@@ -929,7 +929,7 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1042,7 +1042,7 @@
         <v>7</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1155,7 +1155,7 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1381,7 +1381,7 @@
         <v>6</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC9">
         <v>6</v>
@@ -1494,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1607,7 +1607,7 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1720,7 +1720,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1833,7 +1833,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -1860,7 +1860,7 @@
         <v>6</v>
       </c>
       <c r="AK13">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -1946,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>9</v>
@@ -2059,7 +2059,7 @@
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -2404,7 +2404,7 @@
         <v>25</v>
       </c>
       <c r="AB5">
-        <v>90.59999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -2748,7 +2748,7 @@
         <v>95.3</v>
       </c>
       <c r="AB9">
-        <v>93.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>90.59999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -3092,7 +3092,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="AB13">
-        <v>93.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -3264,7 +3264,7 @@
         <v>15.6</v>
       </c>
       <c r="AB15">
-        <v>90.59999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
   </sheetData>
@@ -3330,19 +3330,19 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="G2" s="2">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3648,7 +3648,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3680,7 +3680,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920303</v>
+        <v>23330051920289</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
@@ -3692,10 +3692,10 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3703,16 +3703,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920303</v>
+        <v>23330051920290</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -3726,47 +3726,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920289</v>
+        <v>23330051920303</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920290</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>
